--- a/AnalisisFinanciero/clases/Caso de clase.xlsx
+++ b/AnalisisFinanciero/clases/Caso de clase.xlsx
@@ -7,7 +7,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A3D7E-6709-4FDF-BC47-E70A91AABA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DF006C-6526-43EC-BFD3-1F03EA0235A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
@@ -98,6 +98,18 @@
     <font>
       <name val="Arial Narrow"/>
       <sz val="11.00"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <name val="Arial Narrow"/>
+      <sz val="11.00"/>
+      <color rgb="FF0000FF"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <name val="Arial Narrow"/>
+      <sz val="11.00"/>
       <b/>
       <color rgb="FF000000"/>
       <family val="2"/>
@@ -105,19 +117,7 @@
     <font>
       <name val="Arial Narrow"/>
       <sz val="11.00"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <name val="Arial Narrow"/>
-      <sz val="11.00"/>
       <b/>
-      <color rgb="FF0000FF"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <name val="Arial Narrow"/>
-      <sz val="11.00"/>
       <color rgb="FF0000FF"/>
       <family val="2"/>
     </font>
@@ -143,13 +143,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFE7E6E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -166,26 +166,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -212,17 +192,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -239,6 +208,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -247,45 +247,45 @@
   </borders>
   <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf fontId="1" applyFont="1" fillId="2" applyFill="1"/>
-    <xf fontId="2" applyFont="1" fillId="3" applyFill="1"/>
-    <xf fontId="3" applyFont="1" fillId="4" applyFill="1"/>
-    <xf fontId="2" applyFont="1" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" applyFont="1" borderId="1" applyBorder="1"/>
+    <xf fontId="2" applyFont="1" borderId="2" applyBorder="1"/>
+    <xf fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1"/>
+    <xf fontId="1" applyFont="1" borderId="4" applyBorder="1"/>
+    <xf fontId="1" applyFont="1" borderId="5" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf fontId="2" applyFont="1" borderId="2" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" applyFont="1" borderId="6" applyBorder="1"/>
+    <xf fontId="1" applyFont="1"/>
+    <xf fontId="4" applyFont="1" fillId="3" applyFill="1"/>
+    <xf fontId="5" applyFont="1"/>
+    <xf fontId="2" applyFont="1"/>
+    <xf fontId="1" applyFont="1" borderId="7" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf fontId="2" applyFont="1"/>
-    <xf fontId="2" applyFont="1" borderId="3" applyBorder="1"/>
-    <xf fontId="4" applyFont="1"/>
-    <xf fontId="4" applyFont="1" borderId="4" applyBorder="1"/>
-    <xf fontId="2" applyFont="1" borderId="5" applyBorder="1"/>
-    <xf fontId="5" applyFont="1"/>
-    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1"/>
-    <xf fontId="2" applyFont="1" borderId="7" applyBorder="1"/>
-    <xf fontId="4" applyFont="1" borderId="8" applyBorder="1"/>
+    <xf fontId="2" applyFont="1" borderId="8" applyBorder="1"/>
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1"/>
+    <xf fontId="3" applyFont="1" fillId="5" applyFill="1"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf xfId="13" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="7" applyBorder="1"/>
-    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1"/>
-    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1"/>
-    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" borderId="4" applyBorder="1"/>
-    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="3" applyFill="1"/>
-    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" borderId="4" applyBorder="1"/>
+    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1"/>
+    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1"/>
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="2" applyBorder="1"/>
+    <xf xfId="13" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1"/>
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" borderId="5" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="2" applyBorder="1" applyAlignment="1">
+    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" borderId="7" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="3" applyBorder="1"/>
-    <xf xfId="14" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" borderId="8" applyBorder="1"/>
-    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="5" applyBorder="1"/>
-    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="5" applyFont="1"/>
-    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1"/>
-    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="4" applyFill="1"/>
-    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1"/>
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" borderId="1" applyBorder="1"/>
+    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="8" applyBorder="1"/>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" borderId="6" applyBorder="1"/>
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="5" applyFont="1"/>
+    <xf xfId="14" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="5" applyFill="1"/>
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="3" applyFill="1"/>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="normal" xfId="0" builtinId="0"/>
